--- a/UPMPackages/com.solotopia.nova.framework.kit.network.gamebind/Nova/Tracks/Tracks.xlsx
+++ b/UPMPackages/com.solotopia.nova.framework.kit.network.gamebind/Nova/Tracks/Tracks.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -194,8 +194,21 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -415,8 +428,14 @@
         <fgColor rgb="FFFFF4D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -570,6 +589,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -718,7 +746,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -759,6 +787,16 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1172,433 +1210,426 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="35" customWidth="1" style="1" min="1" max="1"/>
-    <col width="31" customWidth="1" style="1" min="2" max="2"/>
-    <col width="55" customWidth="1" style="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="2" max="2"/>
+    <col width="36" customWidth="1" style="1" min="3" max="3"/>
     <col width="40" customWidth="1" style="1" min="4" max="4"/>
-    <col width="13" customWidth="1" style="1" min="5" max="5"/>
-    <col width="55" customWidth="1" style="1" min="6" max="7"/>
-    <col width="11" customWidth="1" style="1" min="8" max="8"/>
-    <col width="55" customWidth="1" style="1" min="9" max="9"/>
+    <col width="14" customWidth="1" style="1" min="5" max="5"/>
+    <col width="58" customWidth="1" style="1" min="6" max="6"/>
+    <col width="32" customWidth="1" style="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="1" min="8" max="8"/>
+    <col width="48" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1" s="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>事件名</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>事件中文名</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>事件说明</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>属性名</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>属性类型</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>属性说明</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>上报时机</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>目标</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" s="1">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>nova_gamebind_bind</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>直接绑定完成</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>GameBind 为当前账号绑定第三方 OpenID 的请求完成。</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_bind_provider</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>第三方平台。facebook、google、apple、wechat 或 unknown。</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>Bind.BindAsync 请求取得最终结果时上报。</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="21" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="21" t="inlineStr">
         <is>
           <t>直接绑定成功后更新用户属性 nova_openid；冲突与失败不更新。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" s="1">
+    <row r="3">
       <c r="A3" s="12" t="n"/>
       <c r="B3" s="12" t="n"/>
       <c r="C3" s="12" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_bind_result</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>绑定结果。success=成功；conflict=账号归属冲突；failed=其他失败；exception=调用抛出异常。</t>
         </is>
       </c>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="21" t="n"/>
     </row>
-    <row r="4" ht="14.5" customHeight="1" s="1">
+    <row r="4">
       <c r="A4" s="12" t="n"/>
       <c r="B4" s="12" t="n"/>
       <c r="C4" s="12" t="n"/>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_bind_error_code</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>绑定错误码。成功为 0；失败取 NetResponse.ErrorCode；异常为 -1。</t>
         </is>
       </c>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="21" t="n"/>
     </row>
-    <row r="5" ht="14.5" customHeight="1" s="1">
+    <row r="5">
       <c r="A5" s="13" t="n"/>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="13" t="n"/>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_bind_duration_ms</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>绑定调用耗时，单位毫秒，取非负整数。</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="21" t="n"/>
     </row>
-    <row r="6" ht="14.5" customHeight="1" s="1">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>nova_gamebind_query_conflict</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>查询绑定冲突</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>GameBind 查询冲突账号进度摘要的请求完成。</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_query_conflict_result</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>查询结果。success=成功；failed=请求失败；exception=调用抛出异常。</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Bind.QueryConflictAsync 请求取得最终结果时上报。</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>仅记录冲突详情是否成功取得，不上报账号摘要，也不更新 nova_openid。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="14.5" customHeight="1" s="1">
+    <row r="7">
       <c r="A7" s="12" t="n"/>
       <c r="B7" s="12" t="n"/>
       <c r="C7" s="12" t="n"/>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_query_conflict_error_code</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>冲突查询错误码。成功为 0；失败取 NetResponse.ErrorCode；异常为 -1。</t>
         </is>
       </c>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
     </row>
-    <row r="8" ht="14.5" customHeight="1" s="1">
+    <row r="8">
       <c r="A8" s="13" t="n"/>
       <c r="B8" s="13" t="n"/>
       <c r="C8" s="13" t="n"/>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_query_conflict_duration_ms</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>冲突查询调用耗时，单位毫秒，取非负整数。</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1" s="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>nova_gamebind_resolve</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>绑定冲突裁决</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>GameBind 根据玩家选择完成账号归属裁决的请求。</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_resolve_choice</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>玩家选择保留的账号。guest=当前账号；existing=原绑定账号；其他为 unknown。</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>Bind.ResolveAsync 请求取得最终结果时上报。</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>Resolve 成功后先关联响应 final_uid，再将本次 OpenID 写入用户属性 nova_openid。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="14.5" customHeight="1" s="1">
+    <row r="10">
       <c r="A10" s="12" t="n"/>
       <c r="B10" s="12" t="n"/>
       <c r="C10" s="12" t="n"/>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_resolve_has_verify_code</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>是否提供二次验证码；不上传验证码原文。</t>
         </is>
       </c>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
     </row>
-    <row r="11" ht="24" customHeight="1" s="1">
+    <row r="11">
       <c r="A11" s="12" t="n"/>
       <c r="B11" s="12" t="n"/>
       <c r="C11" s="12" t="n"/>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_resolve_result</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>裁决结果。success=成功；conflict=归属冲突；busy=操作繁忙；failed=其他失败；exception=调用抛出异常。</t>
         </is>
       </c>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
     </row>
-    <row r="12" ht="14.5" customHeight="1" s="1">
+    <row r="12">
       <c r="A12" s="12" t="n"/>
       <c r="B12" s="12" t="n"/>
       <c r="C12" s="12" t="n"/>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_resolve_error_code</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>裁决错误码。成功为 0；失败取 NetResponse.ErrorCode；异常为 -1。</t>
         </is>
       </c>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
     </row>
-    <row r="13" ht="14.5" customHeight="1" s="1">
+    <row r="13">
       <c r="A13" s="13" t="n"/>
       <c r="B13" s="13" t="n"/>
       <c r="C13" s="13" t="n"/>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>nova_gamebind_resolve_duration_ms</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>裁决调用耗时，单位毫秒，取非负整数。</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="13" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="I6:I8"/>
+  <autoFilter ref="A1:I13"/>
+  <mergeCells count="9">
     <mergeCell ref="C9:C13"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C2:C5"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B2:B5"/>
     <mergeCell ref="A9:A13"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="I9:I13"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="I2:I5"/>
-    <mergeCell ref="G6:G8"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="G9:G13"/>
     <mergeCell ref="B6:B8"/>
-    <mergeCell ref="H9:H13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
